--- a/data/source/xlsx/Sources.xlsx
+++ b/data/source/xlsx/Sources.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -700,6 +700,65 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>wikidata</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Wikidata</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Wikidata, base di conoscenza libera (Wikimedia Foundation). https://www.wikidata.org</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Wikimedia Foundation</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>repertorio</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Repertorio di un identificatore esterno (owl:sameAs) dell'ancora; usato dalle letture di statuto generate (D-068).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>geonames</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GeoNames</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GeoNames, base di dati geografica. https://www.geonames.org</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>repertorio</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Come sopra (D-068).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/source/xlsx/Sources.xlsx
+++ b/data/source/xlsx/Sources.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -759,6 +759,73 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tci_italia_centrale_1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TCI, Italia centrale I</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Touring Club Italiano, Guida d'Italia, Italia centrale I: carta «Colli Laziali, Monti Lepini ed Ernici», 1:250.000, inserita tra le pp. 480 e 481 (riprodotta in Manzotti 2010, Tav. VI, p. 300).</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Touring Club Italiano</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>carta</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Data dell'edizione da compilare (non registrata nei documenti del progetto).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>igm_150_iii_so</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>IGM, F. 150 III SO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Istituto Geografico Militare, F. 150 III SO, 1:25.000, rilievo 1872, aggiornamenti 1931 e 1940 (riprodotta in Manzotti 2010, Tav. VII, p. 301).</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Istituto Geografico Militare</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1940</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>carta</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Data: ultimo aggiornamento della tavoletta (rilievo 1872).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/source/xlsx/Sources.xlsx
+++ b/data/source/xlsx/Sources.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -826,6 +826,41 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>lugnani_2001</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Lugnani 2001</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Lugnani, L. (2001). Racconto ed esperienza umana del tempo. The Edinburgh Journal of Gadda Studies, 1.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Lucio Lugnani</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2001</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>articolo</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fonte citata di seconda mano, non letta direttamente: la lettura e' estratta da Perosa 2023a, p. 104, n. 97 (D-071).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/source/xlsx/Sources.xlsx
+++ b/data/source/xlsx/Sources.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -861,6 +861,41 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>rr2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>RR II</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Gadda, C. E. (1989). Romanzi e racconti II (G. Pinotti, D. Isella, R. Rodondi, a cura di). Garzanti.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Giorgio Pinotti, Dante Isella, Raffaella Rodondi (a cura di)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1989</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>edizione</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Edizione che contiene QPL (pp. 277–460) e QP: non e' un testimone; QPL e QP vi sono letti (chora:readIn, D-073). Edizione da cui citano Manzotti 2010, Pinotti 2016 e Perosa 2023a.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/source/xlsx/Sources.xlsx
+++ b/data/source/xlsx/Sources.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -896,6 +896,76 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>terzoli_2008</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Terzoli 2008</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Terzoli, M. A. (2008). Riferimento bibliografico completo da compilare (citato in Terzoli 2015, p. 911, per le pp. 109–113).</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Maria Antonietta Terzoli</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2008</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>saggio</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Riferimento completo da compilare (D-080).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>tci_guida_1925</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Guida TCI 1925</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Touring Club Italiano, Guida d'Italia (1925): cartine tra le pp. 736–737 (cart. 4) e 758–759 (cart. 1), citate da Terzoli 2015, p. 911.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Touring Club Italiano</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1925</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>guida, repertorio</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Volume della Guida da precisare. Non collegata alla carta TCI di Manzotti (tci_italia_centrale_1), la cui data resta aperta (D-080).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/source/xlsx/Sources.xlsx
+++ b/data/source/xlsx/Sources.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -689,14 +689,12 @@
           <t>Lorenzo Sabatino</t>
         </is>
       </c>
+      <c r="E9" t="n">
+        <v>2026</v>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>dataset</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Data da compilare (Lorenzo).</t>
         </is>
       </c>
     </row>
@@ -762,32 +760,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tci_italia_centrale_1</t>
+          <t>bertarelli_1924</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TCI, Italia centrale I</t>
+          <t>Bertarelli 1924</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Touring Club Italiano, Guida d'Italia, Italia centrale I: carta «Colli Laziali, Monti Lepini ed Ernici», 1:250.000, inserita tra le pp. 480 e 481 (riprodotta in Manzotti 2010, Tav. VI, p. 300).</t>
+          <t>Bertarelli, L. V. (1924). Italia centrale, vol. I (Guida d'Italia del TCI). Touring Club Italiano.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Touring Club Italiano</t>
-        </is>
+          <t>Luigi Vittorio Bertarelli</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1924</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>carta</t>
+          <t>guida, repertorio</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Data dell'edizione da compilare (non registrata nei documenti del progetto).</t>
+          <t>Cartine: «Colli laziali, Monti Lepini ed Ernici (Roma, Frosinone)», tra pp. 480–481 (Terzoli 2015, CART. 2; la carta di Manzotti 2010, Tav. V/VI, per Casal Bruciato, L-0001; conferma: Terzoli 2015, p. 766); «Sabina meridionale, Monti Tiburtini, Prenestini e Carseolani», tra pp. 456–457 (CART. 3). Le carte sono locatori (D-086).</t>
         </is>
       </c>
     </row>
@@ -927,29 +928,29 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Riferimento completo da compilare (D-080).</t>
+          <t>Terzoli 2015 lo cita come 2007 (p. 419) e 2008 (p. 911), stesse pp. 109–113: anno da verificare. Riferimento bibliografico completo da compilare (D-086).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tci_guida_1925</t>
+          <t>bertarelli_1925</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Guida TCI 1925</t>
+          <t>Bertarelli 1925</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Touring Club Italiano, Guida d'Italia (1925): cartine tra le pp. 736–737 (cart. 4) e 758–759 (cart. 1), citate da Terzoli 2015, p. 911.</t>
+          <t>Bertarelli, L. V. (1925). Roma e dintorni = Italia centrale, vol. IV (Guida d'Italia del TCI). Touring Club Italiano.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Touring Club Italiano</t>
+          <t>Luigi Vittorio Bertarelli</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -962,7 +963,72 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Volume della Guida da precisare. Non collegata alla carta TCI di Manzotti (tci_italia_centrale_1), la cui data resta aperta (D-080).</t>
+          <t>Cartine: «Roma e dintorni», tra pp. 736–737 (Terzoli 2015, CART. 4); «Colli Albani», tra pp. 758–759 (CART. 1). Vi rinvia «TCI, Italia centrale IV, p. 761» di Manzotti 2010, pp. 239–240. Candidata per l'edicola ai Due Santi la CART. 1 (Terzoli 2015, p. 419; DC-03, aperta). Le carte sono locatori (D-086).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>italia_2020</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Italia 2020</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Italia, P. (2020). Editing Duemila: Per una filologia dei testi digitali. Salerno Editrice.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Paola Italia</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>monografia</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>glm_1997a</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Grassadonia, Lagossi e Marchetti 1997a</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Grassadonia, F., Lagossi, P., &amp; Marchetti, M. (a cura di) (1997a). Quer pasticciaccio brutto de via Merulana. Strumenti per la lettura (2 voll.). Milano: Garzanti Scuola.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Fabio Grassadonia; Paola Lagossi; Mario Marchetti</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1997</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>commento</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Citati di seconda mano in Terzoli 2015, pp. 535–537 (chora:originalSource); vale anche per «G.L.M., Commento» citato da Manzotti 2010 (D-086).</t>
         </is>
       </c>
     </row>
